--- a/AAII_Financials/Quarterly/LSEGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LSEGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>LSEGY</t>
   </si>
@@ -656,65 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -748,8 +754,14 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -783,8 +795,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -818,8 +836,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -833,8 +857,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -868,8 +894,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -903,8 +935,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -938,8 +976,14 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -973,8 +1017,14 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -985,8 +1035,10 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1020,8 +1072,14 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1055,8 +1113,14 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1070,8 +1134,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1105,8 +1171,14 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1140,8 +1212,14 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1175,8 +1253,14 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1210,8 +1294,14 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1245,8 +1335,14 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1280,8 +1376,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1315,8 +1417,14 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1350,8 +1458,14 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1385,8 +1499,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1420,8 +1540,14 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1455,8 +1581,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1490,8 +1622,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1525,8 +1663,14 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1560,8 +1704,14 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1595,8 +1745,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1630,48 +1786,60 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1685,8 +1853,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1700,64 +1870,72 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5381500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5355800</v>
+      </c>
+      <c r="F41" s="3">
         <v>5314900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5308200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4729400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4460000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4350400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4657600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4620400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4617400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4560000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4368700</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>246800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>245600</v>
+      </c>
+      <c r="F42" s="3">
         <v>175000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>174700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>290500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>273900</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -1770,43 +1948,55 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3017100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3002800</v>
+      </c>
+      <c r="F43" s="3">
         <v>2534300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2531100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3234700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3050400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2215900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2372300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3294700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3292600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2864700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2744500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1840,183 +2030,219 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1136596800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1131186200</v>
+      </c>
+      <c r="F45" s="3">
         <v>1019383600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1018095500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1059268400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>998927600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>867056800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>928265600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>952937700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>952323900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>972614300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>931808800</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1145599000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1140145600</v>
+      </c>
+      <c r="F46" s="3">
         <v>1027685100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1026386500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1067881900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1007050500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>873896100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>935587700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>960852800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>960233900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>980331900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>939202600</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>188400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>187500</v>
+      </c>
+      <c r="F47" s="3">
         <v>123800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>123700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>104100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>98200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>83900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>89800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>571200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>570900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>509500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>488100</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>923400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>919000</v>
+      </c>
+      <c r="F48" s="3">
         <v>935400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>934200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>789100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>744200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>852600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>912700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>885900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>885300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>912000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>873700</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>41084000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>40888400</v>
+      </c>
+      <c r="F49" s="3">
         <v>42090200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>42037000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>41359100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>39003100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>41276000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>44189800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>41375300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>41348600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>42221200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>40449800</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2050,8 +2276,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2085,43 +2317,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>727100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>723600</v>
+      </c>
+      <c r="F52" s="3">
         <v>663500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>662700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>752200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>709300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>414400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>443600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>539600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>539300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>486600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2155,43 +2399,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1189238400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1183577300</v>
+      </c>
+      <c r="F54" s="3">
         <v>1072279900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1070925100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1111756400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1048425700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>917434300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>982199400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1005080400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1004433000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1025385900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>982366400</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2205,8 +2461,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2220,218 +2478,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2027300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2017700</v>
+      </c>
+      <c r="F57" s="3">
         <v>319000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>318600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2246900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2118900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>404400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>432900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1995500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1994200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>328600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>314800</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4434100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4413000</v>
+      </c>
+      <c r="F58" s="3">
         <v>4495300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>4489600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3429200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3233900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2010600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2152500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3639700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3637400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2835400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2716400</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1137489700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1132074900</v>
+      </c>
+      <c r="F59" s="3">
         <v>1021187100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1019896800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1060372700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>999969000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>868007100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>929282900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>953979000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>953364600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>974314700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>933437900</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1144178100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1138731400</v>
+      </c>
+      <c r="F60" s="3">
         <v>1027611000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1026312600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1066273500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1005533700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>872009500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>933567900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>959734400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>959116200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>978980500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>937907900</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13539900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>13475400</v>
+      </c>
+      <c r="F61" s="3">
         <v>11309600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>11295300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>10302800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>9715900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>10561200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>11306800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10169700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10163200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9623200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>9219500</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>874400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>870200</v>
+      </c>
+      <c r="F62" s="3">
         <v>908500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>907300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>700100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>660200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>711100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>761300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>731700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>731300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>817800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>783400</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2465,8 +2761,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2500,8 +2802,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2535,43 +2843,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1161281700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1155753600</v>
+      </c>
+      <c r="F66" s="3">
         <v>1042444100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1041127000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1079942500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1018424000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>885944600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>948486800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>973450300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>972823300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>992339600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>950706600</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2585,8 +2905,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2620,8 +2942,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2655,8 +2983,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2690,8 +3024,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2725,43 +3065,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15157200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>15085100</v>
+      </c>
+      <c r="F72" s="3">
         <v>1882900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1880500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2193500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2068500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2352400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2518400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2407500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2406000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3715500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3559700</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2795,8 +3147,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2830,8 +3188,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2865,43 +3229,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24812300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>24694100</v>
+      </c>
+      <c r="F76" s="3">
         <v>26852000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>26818000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>28972500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>27322100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>28810500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>30844400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>28798000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>28779500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>30324300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>29052100</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2935,48 +3311,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3010,8 +3398,14 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3025,43 +3419,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>85300</v>
+      </c>
+      <c r="F83" s="3">
         <v>67600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>72400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>83400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>83400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>80200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>76900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>87700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>85400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>58400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3095,8 +3497,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3130,8 +3538,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3165,8 +3579,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3200,8 +3620,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3235,43 +3661,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1184200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1178500</v>
+      </c>
+      <c r="F89" s="3">
         <v>1440100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1438300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1015200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>957400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1359000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1454900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>774100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>773600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1170600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1121500</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3285,43 +3723,51 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-57100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-56800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-41000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-41000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-43200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-40700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-21900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-23500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-24600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-24600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-56700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-54300</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3355,8 +3801,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3390,43 +3842,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-350300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-348600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-923300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-922100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-461700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-435400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-457000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-489200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-346900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-346700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-402500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-385600</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3440,43 +3904,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>338300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>336700</v>
+      </c>
+      <c r="F96" s="3">
         <v>166200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>166000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>322600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>304300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>136500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>146100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>267900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>267800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>124800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>119600</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3510,8 +3982,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3545,8 +4023,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3580,109 +4064,133 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-768900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-765200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-204600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-204300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-518600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-489000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-994000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1064200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-364000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-363700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-712700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-682800</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-21300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-22800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-15200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-15200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-4500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-4300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-69300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-67400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>36100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>70600</v>
+      </c>
+      <c r="F102" s="3">
         <v>334500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>334000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-15800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-14900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-113300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-121300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>48000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>48000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>51000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>48800</v>
       </c>
     </row>
